--- a/tools/_out/brennancad_20261021/regen/stage/tee/DesignTable_6803_SW2.xlsx
+++ b/tools/_out/brennancad_20261021/regen/stage/tee/DesignTable_6803_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ9"/>
+  <dimension ref="A1:BZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,29 +1838,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6803-10-10-10-NWO-FG</t>
+          <t>6803-08-08-06-NWO-FG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="C6" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="E6" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="G6" t="n">
-        <v>0.386</v>
+        <v>0.3295</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1114</v>
+        <v>0.0984</v>
       </c>
       <c r="I6" t="n">
         <v>0.1546</v>
@@ -1872,25 +1872,25 @@
         <v>37</v>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="O6" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.386</v>
+        <v>0.3295</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1114</v>
+        <v>0.0984</v>
       </c>
       <c r="S6" t="n">
         <v>0.1546</v>
@@ -1902,154 +1902,154 @@
         <v>37</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="W6" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4</v>
+        <v>0.2752</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.505</v>
+        <v>0.349</v>
       </c>
       <c r="AB6" t="n">
         <v>75</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.58735</v>
+        <v>0.40722</v>
       </c>
       <c r="AD6" t="n">
         <v>75</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.505</v>
+        <v>0.349</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.5775</v>
+        <v>0.397</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.05</v>
+        <v>0.035</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.3865</v>
+        <v>0.241</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="AK6" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AN6" t="n">
         <v>0.391</v>
       </c>
-      <c r="AL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0.48</v>
-      </c>
       <c r="AO6" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.48</v>
+        <v>0.391</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.48</v>
+        <v>0.297</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.875</v>
+        <v>0.5625</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.391</v>
+        <v>0.312</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.03866</v>
+        <v>0.03007</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.01786</v>
+        <v>0.01389</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.593</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.593</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>6803-10-10-10-NWO-FG</t>
+          <t>6803-08-08-06-NWO-FG</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 7/8-14 JIC x 7/8-14 JIC x 7/8-14 (adjustable male ORB)</t>
+          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 3/4-16 JIC x 3/4-16 JIC x 9/16-18 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>7/8-14 JIC</t>
+          <t>3/4-16 JIC</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>7/8-14 JIC</t>
+          <t>3/4-16 JIC</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>7/8-14 (adjustable male ORB)</t>
+          <t>9/16-18 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2079,49 +2079,49 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>JIC ends VERIFIED (MS33656J); ORB end sourced; legs: Air-Way (MS51529 corroborates same-dash rows) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-CAD 2026-10-21: D3@BORE, HEXB@HEX, LEG3@DRIVE, ORB_GRVDIA@DRIVE, Y@REF, THDMAJ_3@DRIVE, D1@BORE, D2@BORE, LEG1@DRIVE, LEG2@DRIVE, THDMAJ_1@DRIVE, THDMAJ_2@DRIVE, ORB_THDL@DRIVE, ORB_GRVW@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6803-08-08-06-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 3: adjustable ORB tip-to-body-face 1 = Air-Way 6801 ORB_I3 for -10 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6803-08-08-06-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6803-08-08-06-NWO-FG (PARTcommunity / CADENAS, D3@BORE=B3D, HEXB@HEX=C, LEG3@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, Y@REF=Y, THDMAJ_3@DRIVE=B3THD, D1@BORE=B1D, D2@BORE=B2D, LEG1@DRIVE=M1, LEG2@DRIVE=M2, THDMAJ_1@DRIVE=B1THD, THDMAJ_2@DRIVE=B2THD, ORB_THDL@DRIVE=A5, ORB_GRVW@DRIVE=A5; user 2026-10-21 "yes you can use them following my rule") | leg 3: adjustable ORB tip-to-body-face 0.75 = Air-Way 6801 ORB_I3 for -06 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6803-10-10-10-NWO-FG</t>
+          <t>6803-08-08-06-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6803-12-12-12-NWO-FG</t>
+          <t>6803-08-08-10-NWO-FG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="C7" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="D7" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="E7" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4715</v>
+        <v>0.3295</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1299</v>
+        <v>0.0984</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
@@ -2130,28 +2130,28 @@
         <v>37</v>
       </c>
       <c r="L7" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="N7" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="O7" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4715</v>
+        <v>0.3295</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1299</v>
+        <v>0.0984</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="T7" t="n">
         <v>60</v>
@@ -2160,154 +2160,154 @@
         <v>37</v>
       </c>
       <c r="V7" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="W7" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="X7" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.63</v>
+        <v>0.505</v>
       </c>
       <c r="AB7" t="n">
         <v>75</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.73169</v>
+        <v>0.58735</v>
       </c>
       <c r="AD7" t="n">
         <v>75</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.63</v>
+        <v>0.505</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.722</v>
+        <v>0.5775</v>
       </c>
       <c r="AH7" t="n">
         <v>0.05</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.4725</v>
+        <v>0.3865</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.61</v>
+        <v>0.391</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.61</v>
+        <v>0.391</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.61</v>
+        <v>0.484</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.786</v>
+        <v>0.673</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.786</v>
+        <v>0.673</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>6803-12-12-12-NWO-FG</t>
+          <t>6803-08-08-10-NWO-FG</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 1 1/16-12 JIC x 1 1/16-12 JIC x 1 1/16-12 (adjustable male ORB)</t>
+          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 3/4-16 JIC x 3/4-16 JIC x 7/8-14 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -2317,17 +2317,17 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>3/4-16 JIC</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>3/4-16 JIC</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>1 1/16-12 (adjustable male ORB)</t>
+          <t>7/8-14 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -2337,49 +2337,49 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>JIC ends VERIFIED (MS33656J); ORB end sourced; legs: Air-Way (MS51529 corroborates same-dash rows) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-CAD 2026-10-21: D3@BORE, HEXB@HEX, LEG3@DRIVE, ORB_GRVDIA@DRIVE, Y@REF, THDMAJ_3@DRIVE, D1@BORE, D2@BORE, LEG1@DRIVE, LEG2@DRIVE, THDMAJ_1@DRIVE, THDMAJ_2@DRIVE, ORB_THDL@DRIVE, ORB_GRVW@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6803-08-08-10-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>legs differ from MS51529: AW [1.65, 1.65]+boss 1.94 vs MS 1.66/1.94 | hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule); leg 3: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -12 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6803-08-08-10-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6803-08-08-10-NWO-FG (PARTcommunity / CADENAS, D3@BORE=B3D, HEXB@HEX=C, LEG3@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, Y@REF=Y, THDMAJ_3@DRIVE=B3THD, D1@BORE=B1D, D2@BORE=B2D, LEG1@DRIVE=M1, LEG2@DRIVE=M2, THDMAJ_1@DRIVE=B1THD, THDMAJ_2@DRIVE=B2THD, ORB_THDL@DRIVE=A5, ORB_GRVW@DRIVE=A5; user 2026-10-21 "yes you can use them following my rule") | leg 3: adjustable ORB tip-to-body-face 1 = Air-Way 6801 ORB_I3 for -10 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6803-12-12-12-NWO-FG</t>
+          <t>6803-08-08-10-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6803-16-16-16-NWO-FG</t>
+          <t>6803-10-10-10-NWO-FG</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="C8" t="n">
-        <v>0.65625</v>
+        <v>0.44</v>
       </c>
       <c r="D8" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="E8" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4365</v>
+        <v>0.3553</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5965</v>
+        <v>0.386</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1292</v>
+        <v>0.1114</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1858</v>
+        <v>0.1546</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -2388,28 +2388,28 @@
         <v>37</v>
       </c>
       <c r="L8" t="n">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.65625</v>
+        <v>0.44</v>
       </c>
       <c r="N8" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="O8" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4365</v>
+        <v>0.3553</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5965</v>
+        <v>0.386</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1292</v>
+        <v>0.1114</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1858</v>
+        <v>0.1546</v>
       </c>
       <c r="T8" t="n">
         <v>60</v>
@@ -2418,154 +2418,154 @@
         <v>37</v>
       </c>
       <c r="V8" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="W8" t="n">
-        <v>0.65625</v>
+        <v>0.44</v>
       </c>
       <c r="X8" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.755</v>
+        <v>0.505</v>
       </c>
       <c r="AB8" t="n">
         <v>75</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.87603</v>
+        <v>0.58735</v>
       </c>
       <c r="AD8" t="n">
         <v>75</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.755</v>
+        <v>0.505</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.866</v>
+        <v>0.5775</v>
       </c>
       <c r="AH8" t="n">
         <v>0.05</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.5975</v>
+        <v>0.3865</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.3125</v>
+        <v>0.875</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.4365</v>
+        <v>0.3553</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.3125</v>
+        <v>0.875</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.4365</v>
+        <v>0.3553</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.3125</v>
+        <v>0.875</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.3125</v>
+        <v>0.88</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.899</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.899</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.3125</v>
+        <v>0.88</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>6803-16-16-16-NWO-FG</t>
+          <t>6803-10-10-10-NWO-FG</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 1 5/16-12 JIC x 1 5/16-12 JIC x 1 5/16-12 (adjustable male ORB)</t>
+          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 7/8-14 JIC x 7/8-14 JIC x 7/8-14 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -2575,17 +2575,17 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1 5/16-12 JIC</t>
+          <t>7/8-14 JIC</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>1 5/16-12 JIC</t>
+          <t>7/8-14 JIC</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>1 5/16-12 (adjustable male ORB)</t>
+          <t>7/8-14 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -2600,44 +2600,44 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule); leg 3: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -16 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
+          <t>DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 3: adjustable ORB tip-to-body-face 1 = Air-Way 6801 ORB_I3 for -10 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6803-16-16-16-NWO-FG</t>
+          <t>6803-10-10-10-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6803-20-20-20-NWO-FG</t>
+          <t>6803-12-12-12-NWO-FG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="E9" t="n">
         <v>0.125</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4316</v>
+        <v>0.3895</v>
       </c>
       <c r="G9" t="n">
-        <v>0.753</v>
+        <v>0.4715</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1288</v>
+        <v>0.1299</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2382</v>
+        <v>0.1851</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2646,28 +2646,28 @@
         <v>37</v>
       </c>
       <c r="L9" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="O9" t="n">
         <v>0.125</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4316</v>
+        <v>0.3895</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.753</v>
+        <v>0.4715</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1288</v>
+        <v>0.1299</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2382</v>
+        <v>0.1851</v>
       </c>
       <c r="T9" t="n">
         <v>60</v>
@@ -2676,28 +2676,28 @@
         <v>37</v>
       </c>
       <c r="V9" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>0.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="Z9" t="n">
         <v>0.027</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.945</v>
+        <v>0.63</v>
       </c>
       <c r="AB9" t="n">
         <v>75</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.09542</v>
+        <v>0.73169</v>
       </c>
       <c r="AD9" t="n">
         <v>75</v>
@@ -2706,55 +2706,55 @@
         <v>0.41</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.945</v>
+        <v>0.63</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.0825</v>
+        <v>0.722</v>
       </c>
       <c r="AH9" t="n">
         <v>0.05</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.4725</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="AK9" t="n">
         <v>0.469</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.88</v>
+        <v>1.25</v>
       </c>
       <c r="AM9" t="n">
         <v>0.41</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.08</v>
+        <v>0.61</v>
       </c>
       <c r="AO9" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.08</v>
+        <v>0.61</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.08</v>
+        <v>0.61</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.625</v>
+        <v>1.0625</v>
       </c>
       <c r="AU9" t="n">
         <v>0.08333</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.4316</v>
+        <v>0.3895</v>
       </c>
       <c r="AW9" t="n">
         <v>0.04511</v>
@@ -2766,13 +2766,13 @@
         <v>0.08333</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.625</v>
+        <v>1.0625</v>
       </c>
       <c r="BA9" t="n">
         <v>0.08333</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.4316</v>
+        <v>0.3895</v>
       </c>
       <c r="BC9" t="n">
         <v>0.04511</v>
@@ -2784,7 +2784,7 @@
         <v>0.08333</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.625</v>
+        <v>1.0625</v>
       </c>
       <c r="BG9" t="n">
         <v>0.08333</v>
@@ -2802,68 +2802,842 @@
         <v>0.08333</v>
       </c>
       <c r="BL9" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>6803-12-12-12-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 1 1/16-12 JIC x 1 1/16-12 JIC x 1 1/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>6803</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>JIC ends VERIFIED (MS33656J); ORB end sourced; legs: Air-Way (MS51529 corroborates same-dash rows) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>legs differ from MS51529: AW [1.65, 1.65]+boss 1.94 vs MS 1.66/1.94 | hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule); leg 3: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -12 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>6803-12-12-12-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6803-16-16-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="J10" t="n">
+        <v>60</v>
+      </c>
+      <c r="K10" t="n">
+        <v>37</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="T10" t="n">
+        <v>60</v>
+      </c>
+      <c r="U10" t="n">
+        <v>37</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.87603</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.5975</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>6803-16-16-16-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 1 5/16-12 JIC x 1 5/16-12 JIC x 1 5/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>6803</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>1 5/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>1 5/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>JIC ends VERIFIED (MS33656J); ORB end sourced; legs: Air-Way (MS51529 corroborates same-dash rows) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule); leg 3: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -16 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>6803-16-16-16-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6803-20-20-20-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="J11" t="n">
+        <v>60</v>
+      </c>
+      <c r="K11" t="n">
+        <v>37</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="T11" t="n">
+        <v>60</v>
+      </c>
+      <c r="U11" t="n">
+        <v>37</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.09542</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.0825</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.7534999999999999</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BL11" t="n">
         <v>1.63</v>
       </c>
-      <c r="BM9" t="n">
+      <c r="BM11" t="n">
         <v>1.102</v>
       </c>
-      <c r="BN9" t="n">
+      <c r="BN11" t="n">
         <v>1.102</v>
       </c>
-      <c r="BO9" t="n">
+      <c r="BO11" t="n">
         <v>1.63</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BP11" t="n">
         <v>1.11</v>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
         <is>
           <t>6803-20-20-20-NWO-FG</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BR11" t="inlineStr">
         <is>
           <t>Male JIC Run x Adjustable Male ORB Branch Tee, 1 5/8-12 JIC x 1 5/8-12 JIC x 1 5/8-12 (adjustable male ORB)</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>6803</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>1 5/8-12 JIC</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>1 5/8-12 JIC</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>1 5/8-12 (adjustable male ORB)</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>JIC ends VERIFIED (MS33656J); ORB end sourced; legs: Air-Way (MS51529 corroborates same-dash rows) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 3: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -20 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>6803-20-20-20-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6803-24-24-24-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="J12" t="n">
+        <v>60</v>
+      </c>
+      <c r="K12" t="n">
+        <v>37</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="T12" t="n">
+        <v>60</v>
+      </c>
+      <c r="U12" t="n">
+        <v>37</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.0675</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.23687</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.0675</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>6803-24-24-24-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>Male JIC Run x Adjustable Male ORB Branch Tee, 1 7/8-12 JIC x 1 7/8-12 JIC x 1 7/8-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>6803</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>1 7/8-12 JIC</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>1 7/8-12 JIC</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21: D3@BORE, HEXB@HEX, LEG3@DRIVE, ORB_GRVDIA@DRIVE, Y@REF, THDMAJ_3@DRIVE, D1@BORE, D2@BORE, LEG1@DRIVE, LEG2@DRIVE, THDMAJ_1@DRIVE, THDMAJ_2@DRIVE, ORB_THDL@DRIVE, ORB_GRVW@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6803-24-24-24-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6803-24-24-24-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6803-24-24-24-NWO-FG (PARTcommunity / CADENAS, D3@BORE=B3D, HEXB@HEX=C, LEG3@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, Y@REF=Y, THDMAJ_3@DRIVE=B3THD, D1@BORE=B1D, D2@BORE=B2D, LEG1@DRIVE=M1, LEG2@DRIVE=M2, THDMAJ_1@DRIVE=B1THD, THDMAJ_2@DRIVE=B2THD, ORB_THDL@DRIVE=A5, ORB_GRVW@DRIVE=A5; user 2026-10-21 "yes you can use them following my rule") | leg 3: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -24 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>6803-24-24-24-NWO-FG</t>
         </is>
       </c>
     </row>
